--- a/survey_templates/043_reintegration_knowledge_quiz--survey_templates.xlsx
+++ b/survey_templates/043_reintegration_knowledge_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>page_1</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>What is the reintegration process?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>reintegration_process</t>
+          <t>What are common barriers to reintegration?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_1_hint</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>reintegration_process_hint</t>
+          <t>When do you know if someone needs help?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>example</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>barriers</t>
+          <t>Example of reintegration in action</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>needs_assessment</t>
+          <t>Reintegration process explanation</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>example</t>
+          <t>Barriers to reintegration</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>reintegration_process</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>reintegration_process</t>
+          <t>Needs assessment for reintegration</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>barriers</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>barriers</t>
+          <t>Example of a reconnected individual</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>needs_assessment</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>needs_assessment</t>
+          <t>Additional feedback or comments</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,21 +745,90 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>example</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>example</t>
+          <t>Demographic information</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>question_10</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>question_11</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>question_12</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -776,10 +845,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
@@ -804,544 +873,476 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_1_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1_-_what_is_the_reintegration_process?</t>
+          <t>reunification_and_reconnection</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1 - What is the reintegration process?</t>
+          <t>Reunification and reconnection</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_1_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2_-_what_are_some_common_barriers_to_reintegration?</t>
+          <t>rebuilding</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2 - What are some common barriers to reintegration?</t>
+          <t>Rebuilding</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page_1_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3_-_how_do_you_know_if_someone_needs_help?</t>
+          <t>integration_and_assimilation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3 - How do you know if someone needs help?</t>
+          <t>Integration and assimilation</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>page_1_choices</t>
+          <t>question_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4_-_what_is_an_example_of_reintegration_in_action?</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4 - What is an example of reintegration in action?</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>reunification_and_reconnection</t>
+          <t>limited_financial_resources</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Reunification and reconnection</t>
+          <t>Limited financial resources</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>reintegration_and_rebuilding</t>
+          <t>lack_of_family_support</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reintegration and rebuilding</t>
+          <t>Lack of family support</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>integration_and_assimilation</t>
+          <t>social_stigma</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Integration and assimilation</t>
+          <t>Social stigma</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>none_of_the_above</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1_-_limited_financial_resources</t>
+          <t>they_have_difficulty_accessing_basic_needs</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1 - Limited financial resources</t>
+          <t>They have difficulty accessing basic needs</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2_-_lack_of_family_support</t>
+          <t>they_have_difficulty_accessing_specialized_support</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2 - Lack of family support</t>
+          <t>They have difficulty accessing specialized support</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3_-_social_stigma</t>
+          <t>they_have_difficulty_in_accessing_other_services</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3 - Social stigma</t>
+          <t>They have difficulty in accessing other services</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4_-_none_of_the_above</t>
+          <t>they_have_no_need_for_help</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4 - None of the above</t>
+          <t>They have no need for help</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>example_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1_-_they_have_difficulty_accessing_basic_needs</t>
+          <t>family_reunification</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1 - They have difficulty accessing basic needs</t>
+          <t>Family reunification</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>example_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2_-_they_have_difficulty_accessing_specialized_support</t>
+          <t>reconnection</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2 - They have difficulty accessing specialized support</t>
+          <t>Reconnection</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>example_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3_-_they_have_difficulty_in_accessing_other_services</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3 - They have difficulty in accessing other services</t>
+          <t>Integration</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>example_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4_-_they_have_no_need_for_help</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4 - They have no need for help</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1_-_family_reunification</t>
+          <t>limited_financial_resources</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1 - Family reunification</t>
+          <t>Limited financial resources</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2_-_reconnection</t>
+          <t>lack_of_family_support</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2 - Reconnection</t>
+          <t>Lack of family support</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3_-_integration</t>
+          <t>social_stigma</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3 - Integration</t>
+          <t>Social stigma</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4_-_none_of_the_above</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4 - None of the above</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>barriers_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1_-_limited_financial_resources</t>
+          <t>they_have_difficulty_accessing_basic_needs</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1 - Limited financial resources</t>
+          <t>They have difficulty accessing basic needs</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>barriers_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2_-_lack_of_family_support</t>
+          <t>they_have_difficulty_accessing_specialized_support</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2 - Lack of family support</t>
+          <t>They have difficulty accessing specialized support</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>barriers_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3_-_social_stigma</t>
+          <t>they_have_difficulty_accessing_other_services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3 - Social stigma</t>
+          <t>They have difficulty accessing other services</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>barriers_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4_-_none_of_the_above</t>
+          <t>they_have_no_need_for_help</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>4 - None of the above</t>
+          <t>They have no need for help</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>needs_assessment_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1_-_they_have_difficulty_accessing_basic_needs</t>
+          <t>family_reunification</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1 - They have difficulty accessing basic needs</t>
+          <t>Family reunification</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>needs_assessment_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2_-_they_have_difficulty_accessing_specialized_support</t>
+          <t>reconnection</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2 - They have difficulty accessing specialized support</t>
+          <t>Reconnection</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>needs_assessment_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3_-_they_have_difficulty_accessing_other_services</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3 - They have difficulty accessing other services</t>
+          <t>Integration</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>needs_assessment_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4_-_they_have_no_need_for_help</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>4 - They have no need for help</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>example_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1_-_family_reunification</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1 - Family reunification</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>example_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2_-_reconnection</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2 - Reconnection</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>example_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3_-_integration</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>3 - Integration</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>example_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4_-_none_of_the_above</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>4 - None of the above</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
